--- a/PV_ICE/baselines/SupportingMaterial/DegradationRateCheck.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/DegradationRateCheck.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A432A4A9-7562-4406-A456-B5A4BB6104E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE0CEF6-795A-433F-B1FD-0A2D2F0C5CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6540" yWindow="0" windowWidth="7650" windowHeight="15585" xr2:uid="{B3EBB2B5-A1FC-4A33-ABDE-ED0E11498B1D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B3EBB2B5-A1FC-4A33-ABDE-ED0E11498B1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PLOSOnePaperDegTable" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>years</t>
   </si>
@@ -54,6 +55,27 @@
   </si>
   <si>
     <t>0.75, 0.76</t>
+  </si>
+  <si>
+    <t>T50</t>
+  </si>
+  <si>
+    <t>T90</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>[years]</t>
+  </si>
+  <si>
+    <t>[%/yr]</t>
+  </si>
+  <si>
+    <t>Project Lifetime</t>
   </si>
 </sst>
 </file>
@@ -482,7 +504,7 @@
         <v>100</v>
       </c>
       <c r="C2" s="1">
-        <v>1.3</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -491,11 +513,11 @@
       </c>
       <c r="B3" s="2">
         <f t="shared" ref="B3:B66" si="0">B2*(1-C$3)</f>
-        <v>98.7</v>
+        <v>99.17</v>
       </c>
       <c r="C3">
         <f>C2/100</f>
-        <v>1.3000000000000001E-2</v>
+        <v>8.3000000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -504,7 +526,7 @@
       </c>
       <c r="B4" s="2">
         <f t="shared" si="0"/>
-        <v>97.416899999999998</v>
+        <v>98.346889000000004</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -513,7 +535,7 @@
       </c>
       <c r="B5" s="2">
         <f t="shared" si="0"/>
-        <v>96.150480299999998</v>
+        <v>97.530609821300004</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -522,7 +544,7 @@
       </c>
       <c r="B6" s="2">
         <f t="shared" si="0"/>
-        <v>94.900524056099997</v>
+        <v>96.721105759783214</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
@@ -534,7 +556,7 @@
       </c>
       <c r="B7" s="2">
         <f t="shared" si="0"/>
-        <v>93.666817243370701</v>
+        <v>95.918320581977014</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -546,7 +568,7 @@
       </c>
       <c r="B8" s="2">
         <f t="shared" si="0"/>
-        <v>92.449148619206881</v>
+        <v>95.122198521146601</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -558,7 +580,7 @@
       </c>
       <c r="B9" s="2">
         <f t="shared" si="0"/>
-        <v>91.247309687157184</v>
+        <v>94.33268427342108</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -570,7 +592,7 @@
       </c>
       <c r="B10" s="2">
         <f t="shared" si="0"/>
-        <v>90.061094661224146</v>
+        <v>93.54972299395169</v>
       </c>
       <c r="C10">
         <v>2.5</v>
@@ -582,7 +604,7 @@
       </c>
       <c r="B11" s="2">
         <f t="shared" si="0"/>
-        <v>88.89030043062823</v>
+        <v>92.773260293101899</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -591,7 +613,7 @@
       </c>
       <c r="B12" s="2">
         <f t="shared" si="0"/>
-        <v>87.734726525030055</v>
+        <v>92.003242232669152</v>
       </c>
       <c r="C12">
         <v>2.1</v>
@@ -603,7 +625,7 @@
       </c>
       <c r="B13" s="2">
         <f t="shared" si="0"/>
-        <v>86.594175080204664</v>
+        <v>91.239615322137993</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -615,7 +637,7 @@
       </c>
       <c r="B14" s="2">
         <f t="shared" si="0"/>
-        <v>85.468450804162003</v>
+        <v>90.482326514964257</v>
       </c>
       <c r="C14">
         <v>1.8</v>
@@ -627,7 +649,7 @@
       </c>
       <c r="B15" s="2">
         <f t="shared" si="0"/>
-        <v>84.357360943707903</v>
+        <v>89.73132320489006</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -636,7 +658,7 @@
       </c>
       <c r="B16" s="2">
         <f t="shared" si="0"/>
-        <v>83.260715251439706</v>
+        <v>88.986553222289473</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -645,7 +667,7 @@
       </c>
       <c r="B17" s="2">
         <f t="shared" si="0"/>
-        <v>82.178325953170983</v>
+        <v>88.247964830544475</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -657,7 +679,7 @@
       </c>
       <c r="B18" s="2">
         <f t="shared" si="0"/>
-        <v>81.110007715779759</v>
+        <v>87.515506722450965</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -666,7 +688,7 @@
       </c>
       <c r="B19" s="2">
         <f t="shared" si="0"/>
-        <v>80.055577615474618</v>
+        <v>86.78912801665463</v>
       </c>
       <c r="C19">
         <v>1.3</v>
@@ -678,7 +700,7 @@
       </c>
       <c r="B20" s="2">
         <f t="shared" si="0"/>
-        <v>79.014855106473448</v>
+        <v>86.068778254116395</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -687,7 +709,7 @@
       </c>
       <c r="B21" s="2">
         <f t="shared" si="0"/>
-        <v>77.987661990089293</v>
+        <v>85.354407394607236</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -696,7 +718,7 @@
       </c>
       <c r="B22" s="2">
         <f t="shared" si="0"/>
-        <v>76.973822384218138</v>
+        <v>84.645965813231996</v>
       </c>
       <c r="C22">
         <v>1.1000000000000001</v>
@@ -708,7 +730,7 @@
       </c>
       <c r="B23" s="2">
         <f t="shared" si="0"/>
-        <v>75.973162693223301</v>
+        <v>83.943404296982166</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -717,7 +739,7 @@
       </c>
       <c r="B24" s="2">
         <f t="shared" si="0"/>
-        <v>74.985511578211401</v>
+        <v>83.24667404131722</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -729,7 +751,7 @@
       </c>
       <c r="B25" s="2">
         <f t="shared" si="0"/>
-        <v>74.010699927694645</v>
+        <v>82.555726646774289</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -738,7 +760,7 @@
       </c>
       <c r="B26" s="2">
         <f t="shared" si="0"/>
-        <v>73.048560828634621</v>
+        <v>81.870514115606071</v>
       </c>
       <c r="C26" s="3">
         <v>0.9</v>
@@ -750,7 +772,7 @@
       </c>
       <c r="B27" s="2">
         <f t="shared" si="0"/>
-        <v>72.098929537862375</v>
+        <v>81.190988848446537</v>
       </c>
       <c r="C27">
         <v>0.86</v>
@@ -762,7 +784,10 @@
       </c>
       <c r="B28" s="2">
         <f t="shared" si="0"/>
-        <v>71.16164345387017</v>
+        <v>80.517103641004439</v>
+      </c>
+      <c r="C28">
+        <v>0.83</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -771,7 +796,7 @@
       </c>
       <c r="B29" s="2">
         <f t="shared" si="0"/>
-        <v>70.236542088969856</v>
+        <v>79.84881168078411</v>
       </c>
       <c r="C29" s="3">
         <v>0.8</v>
@@ -783,7 +808,7 @@
       </c>
       <c r="B30" s="2">
         <f t="shared" si="0"/>
-        <v>69.323467041813245</v>
+        <v>79.186066543833604</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -792,7 +817,7 @@
       </c>
       <c r="B31" s="2">
         <f t="shared" si="0"/>
-        <v>68.422261970269673</v>
+        <v>78.528822191519794</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -804,7 +829,7 @@
       </c>
       <c r="B32" s="2">
         <f t="shared" si="0"/>
-        <v>67.53277256465617</v>
+        <v>77.87703296733018</v>
       </c>
       <c r="C32">
         <v>0.73</v>
@@ -816,7 +841,7 @@
       </c>
       <c r="B33" s="2">
         <f t="shared" si="0"/>
-        <v>66.654846521315633</v>
+        <v>77.230653593701348</v>
       </c>
       <c r="C33" s="3">
         <v>0.7</v>
@@ -828,7 +853,7 @@
       </c>
       <c r="B34" s="2">
         <f t="shared" si="0"/>
-        <v>65.788333516538529</v>
+        <v>76.589639168873632</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -837,7 +862,7 @@
       </c>
       <c r="B35" s="2">
         <f t="shared" si="0"/>
-        <v>64.933085180823525</v>
+        <v>75.953945163771976</v>
       </c>
       <c r="C35">
         <v>0.66700000000000004</v>
@@ -849,7 +874,7 @@
       </c>
       <c r="B36" s="2">
         <f t="shared" si="0"/>
-        <v>64.088955073472818</v>
+        <v>75.323527418912676</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -858,7 +883,7 @@
       </c>
       <c r="B37" s="2">
         <f t="shared" si="0"/>
-        <v>63.255798657517673</v>
+        <v>74.698342141335701</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -867,7 +892,7 @@
       </c>
       <c r="B38" s="2">
         <f t="shared" si="0"/>
-        <v>62.433473274969941</v>
+        <v>74.078345901562614</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -876,7 +901,7 @@
       </c>
       <c r="B39" s="2">
         <f t="shared" si="0"/>
-        <v>61.621838122395332</v>
+        <v>73.463495630579644</v>
       </c>
       <c r="C39" s="3">
         <v>0.6</v>
@@ -888,7 +913,7 @@
       </c>
       <c r="B40" s="2">
         <f t="shared" si="0"/>
-        <v>60.820754226804191</v>
+        <v>72.853748616845834</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -897,7 +922,7 @@
       </c>
       <c r="B41" s="2">
         <f t="shared" si="0"/>
-        <v>60.030084421855733</v>
+        <v>72.249062503326016</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -906,7 +931,7 @@
       </c>
       <c r="B42" s="2">
         <f t="shared" si="0"/>
-        <v>59.249693324371606</v>
+        <v>71.649395284548419</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -915,7 +940,7 @@
       </c>
       <c r="B43" s="2">
         <f t="shared" si="0"/>
-        <v>58.479447311154772</v>
+        <v>71.054705303686674</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -924,7 +949,7 @@
       </c>
       <c r="B44" s="2">
         <f t="shared" si="0"/>
-        <v>57.719214496109757</v>
+        <v>70.464951249666072</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -933,7 +958,7 @@
       </c>
       <c r="B45" s="2">
         <f t="shared" si="0"/>
-        <v>56.96886470766033</v>
+        <v>69.880092154293848</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -942,7 +967,7 @@
       </c>
       <c r="B46" s="2">
         <f t="shared" si="0"/>
-        <v>56.228269466460745</v>
+        <v>69.300087389413207</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -951,7 +976,7 @@
       </c>
       <c r="B47" s="2">
         <f t="shared" si="0"/>
-        <v>55.497301963396751</v>
+        <v>68.724896664081072</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -960,7 +985,7 @@
       </c>
       <c r="B48" s="2">
         <f t="shared" si="0"/>
-        <v>54.775837037872591</v>
+        <v>68.154480021769203</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -969,7 +994,7 @@
       </c>
       <c r="B49" s="2">
         <f t="shared" si="0"/>
-        <v>54.063751156380249</v>
+        <v>67.588797837588515</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -978,7 +1003,7 @@
       </c>
       <c r="B50" s="2">
         <f t="shared" si="0"/>
-        <v>53.360922391347309</v>
+        <v>67.027810815536526</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -987,7 +1012,7 @@
       </c>
       <c r="B51" s="2">
         <f t="shared" si="0"/>
-        <v>52.66723040025979</v>
+        <v>66.471479985767573</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -996,7 +1021,7 @@
       </c>
       <c r="B52" s="2">
         <f t="shared" si="0"/>
-        <v>51.982556405056414</v>
+        <v>65.919766701885706</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -1005,7 +1030,7 @@
       </c>
       <c r="B53" s="2">
         <f t="shared" si="0"/>
-        <v>51.306783171790677</v>
+        <v>65.372632638260058</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -1014,7 +1039,7 @@
       </c>
       <c r="B54" s="2">
         <f t="shared" si="0"/>
-        <v>50.639794990557398</v>
+        <v>64.830039787362495</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -1023,7 +1048,7 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" si="0"/>
-        <v>49.981477655680152</v>
+        <v>64.291950457127385</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -1032,7 +1057,7 @@
       </c>
       <c r="B56" s="2">
         <f t="shared" si="0"/>
-        <v>49.331718446156309</v>
+        <v>63.758327268333232</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -1041,7 +1066,7 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" si="0"/>
-        <v>48.690406106356278</v>
+        <v>63.229133152006071</v>
       </c>
       <c r="C57">
         <v>0.4</v>
@@ -1053,7 +1078,7 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="0"/>
-        <v>48.057430826973643</v>
+        <v>62.70433134684442</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -1062,7 +1087,7 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" si="0"/>
-        <v>47.432684226222989</v>
+        <v>62.183885396665616</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -1071,7 +1096,7 @@
       </c>
       <c r="B60" s="2">
         <f t="shared" si="0"/>
-        <v>46.816059331282091</v>
+        <v>61.667759147873291</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -1080,7 +1105,7 @@
       </c>
       <c r="B61" s="2">
         <f t="shared" si="0"/>
-        <v>46.20745055997542</v>
+        <v>61.155916746945941</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -1089,7 +1114,7 @@
       </c>
       <c r="B62" s="2">
         <f t="shared" si="0"/>
-        <v>45.606753702695741</v>
+        <v>60.648322637946293</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -1098,7 +1123,7 @@
       </c>
       <c r="B63" s="2">
         <f t="shared" si="0"/>
-        <v>45.013865904560696</v>
+        <v>60.144941560051343</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -1107,7 +1132,7 @@
       </c>
       <c r="B64" s="2">
         <f t="shared" si="0"/>
-        <v>44.428685647801409</v>
+        <v>59.645738545102915</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -1116,7 +1141,7 @@
       </c>
       <c r="B65" s="2">
         <f t="shared" si="0"/>
-        <v>43.851112734379988</v>
+        <v>59.15067891517856</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
@@ -1125,7 +1150,7 @@
       </c>
       <c r="B66" s="2">
         <f t="shared" si="0"/>
-        <v>43.281048268833047</v>
+        <v>58.659728280182577</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -1134,7 +1159,7 @@
       </c>
       <c r="B67" s="2">
         <f t="shared" ref="B67:B94" si="1">B66*(1-C$3)</f>
-        <v>42.718394641338215</v>
+        <v>58.172852535457061</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
@@ -1143,7 +1168,7 @@
       </c>
       <c r="B68" s="2">
         <f t="shared" si="1"/>
-        <v>42.16305551100082</v>
+        <v>57.690017859412769</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
@@ -1152,7 +1177,7 @@
       </c>
       <c r="B69" s="2">
         <f t="shared" si="1"/>
-        <v>41.614935789357808</v>
+        <v>57.211190711179647</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -1161,7 +1186,7 @@
       </c>
       <c r="B70" s="2">
         <f t="shared" si="1"/>
-        <v>41.073941624096157</v>
+        <v>56.736337828276859</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -1170,7 +1195,7 @@
       </c>
       <c r="B71" s="2">
         <f t="shared" si="1"/>
-        <v>40.539980382982904</v>
+        <v>56.265426224302161</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
@@ -1179,7 +1204,7 @@
       </c>
       <c r="B72" s="2">
         <f t="shared" si="1"/>
-        <v>40.012960638004124</v>
+        <v>55.798423186640456</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -1188,7 +1213,7 @@
       </c>
       <c r="B73" s="2">
         <f t="shared" si="1"/>
-        <v>39.49279214971007</v>
+        <v>55.335296274191343</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -1197,7 +1222,7 @@
       </c>
       <c r="B74" s="2">
         <f t="shared" si="1"/>
-        <v>38.979385851763837</v>
+        <v>54.876013315115557</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -1206,7 +1231,7 @@
       </c>
       <c r="B75" s="2">
         <f t="shared" si="1"/>
-        <v>38.472653835690906</v>
+        <v>54.420542404600099</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -1215,7 +1240,7 @@
       </c>
       <c r="B76" s="2">
         <f t="shared" si="1"/>
-        <v>37.972509335826921</v>
+        <v>53.968851902641916</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -1224,7 +1249,7 @@
       </c>
       <c r="B77" s="2">
         <f t="shared" si="1"/>
-        <v>37.478866714461169</v>
+        <v>53.520910431849991</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -1233,7 +1258,7 @@
       </c>
       <c r="B78" s="2">
         <f t="shared" si="1"/>
-        <v>36.991641447173173</v>
+        <v>53.076686875265636</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -1242,7 +1267,7 @@
       </c>
       <c r="B79" s="2">
         <f t="shared" si="1"/>
-        <v>36.510750108359922</v>
+        <v>52.63615037420093</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -1251,7 +1276,7 @@
       </c>
       <c r="B80" s="2">
         <f t="shared" si="1"/>
-        <v>36.036110356951241</v>
+        <v>52.199270326095061</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
@@ -1260,7 +1285,7 @@
       </c>
       <c r="B81" s="2">
         <f t="shared" si="1"/>
-        <v>35.567640922310872</v>
+        <v>51.766016382388472</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
@@ -1269,7 +1294,7 @@
       </c>
       <c r="B82" s="2">
         <f t="shared" si="1"/>
-        <v>35.105261590320829</v>
+        <v>51.33635844641465</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
@@ -1278,7 +1303,7 @@
       </c>
       <c r="B83" s="2">
         <f t="shared" si="1"/>
-        <v>34.648893189646657</v>
+        <v>50.910266671309408</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
@@ -1287,7 +1312,7 @@
       </c>
       <c r="B84" s="2">
         <f t="shared" si="1"/>
-        <v>34.198457578181248</v>
+        <v>50.487711457937543</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -1296,7 +1321,7 @@
       </c>
       <c r="B85" s="2">
         <f t="shared" si="1"/>
-        <v>33.753877629664892</v>
+        <v>50.06866345283666</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
@@ -1305,7 +1330,7 @@
       </c>
       <c r="B86" s="2">
         <f t="shared" si="1"/>
-        <v>33.315077220479246</v>
+        <v>49.65309354617812</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
@@ -1314,7 +1339,7 @@
       </c>
       <c r="B87" s="2">
         <f t="shared" si="1"/>
-        <v>32.881981216613013</v>
+        <v>49.240972869744844</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
@@ -1323,7 +1348,7 @@
       </c>
       <c r="B88" s="2">
         <f t="shared" si="1"/>
-        <v>32.454515460797047</v>
+        <v>48.832272794925963</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
@@ -1332,7 +1357,7 @@
       </c>
       <c r="B89" s="2">
         <f t="shared" si="1"/>
-        <v>32.032606759806683</v>
+        <v>48.426964930728076</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
@@ -1341,7 +1366,7 @@
       </c>
       <c r="B90" s="2">
         <f t="shared" si="1"/>
-        <v>31.616182871929194</v>
+        <v>48.025021121803036</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
@@ -1350,7 +1375,7 @@
       </c>
       <c r="B91" s="2">
         <f t="shared" si="1"/>
-        <v>31.205172494594112</v>
+        <v>47.626413446492073</v>
       </c>
       <c r="C91">
         <v>0.25</v>
@@ -1362,7 +1387,7 @@
       </c>
       <c r="B92" s="2">
         <f t="shared" si="1"/>
-        <v>30.799505252164387</v>
+        <v>47.23111421488619</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
@@ -1371,7 +1396,7 @@
       </c>
       <c r="B93" s="2">
         <f t="shared" si="1"/>
-        <v>30.39911168388625</v>
+        <v>46.839095966902633</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
@@ -1380,7 +1405,7 @@
       </c>
       <c r="B94" s="2">
         <f t="shared" si="1"/>
-        <v>30.003923231995728</v>
+        <v>46.450331470377343</v>
       </c>
     </row>
   </sheetData>
@@ -1396,4 +1421,377 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4414BE69-DEC3-4890-9AFA-FEEF76E6C81E}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>1.47</v>
+      </c>
+      <c r="C3">
+        <v>13.95</v>
+      </c>
+      <c r="D3">
+        <v>19.78</v>
+      </c>
+      <c r="E3">
+        <v>3.44</v>
+      </c>
+      <c r="F3">
+        <v>15.52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>1.22</v>
+      </c>
+      <c r="C4">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="D4">
+        <v>23.15</v>
+      </c>
+      <c r="E4">
+        <v>4.34</v>
+      </c>
+      <c r="F4">
+        <v>19.11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>21</v>
+      </c>
+      <c r="B5">
+        <v>1.05</v>
+      </c>
+      <c r="C5">
+        <v>21.17</v>
+      </c>
+      <c r="D5">
+        <v>26.53</v>
+      </c>
+      <c r="E5">
+        <v>5.32</v>
+      </c>
+      <c r="F5">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>24</v>
+      </c>
+      <c r="B6">
+        <v>0.92</v>
+      </c>
+      <c r="C6">
+        <v>24.78</v>
+      </c>
+      <c r="D6">
+        <v>29.9</v>
+      </c>
+      <c r="E6">
+        <v>6.39</v>
+      </c>
+      <c r="F6">
+        <v>26.24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>27</v>
+      </c>
+      <c r="B7">
+        <v>0.82</v>
+      </c>
+      <c r="C7">
+        <v>28.39</v>
+      </c>
+      <c r="D7">
+        <v>33.28</v>
+      </c>
+      <c r="E7">
+        <v>7.55</v>
+      </c>
+      <c r="F7">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>0.74</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>36.65</v>
+      </c>
+      <c r="E8">
+        <v>8.85</v>
+      </c>
+      <c r="F8">
+        <v>33.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.69</v>
+      </c>
+      <c r="C9">
+        <v>34.409999999999997</v>
+      </c>
+      <c r="D9">
+        <v>38.9</v>
+      </c>
+      <c r="E9">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="F9">
+        <v>35.72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>34</v>
+      </c>
+      <c r="B10">
+        <v>0.65</v>
+      </c>
+      <c r="C10">
+        <v>36.81</v>
+      </c>
+      <c r="D10">
+        <v>41.15</v>
+      </c>
+      <c r="E10">
+        <v>10.77</v>
+      </c>
+      <c r="F10">
+        <v>38.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>36</v>
+      </c>
+      <c r="B11">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="C11">
+        <v>39.22</v>
+      </c>
+      <c r="D11">
+        <v>43.4</v>
+      </c>
+      <c r="E11">
+        <v>11.85</v>
+      </c>
+      <c r="F11">
+        <v>40.450000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>38</v>
+      </c>
+      <c r="B12">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="C12">
+        <v>41.63</v>
+      </c>
+      <c r="D12">
+        <v>45.65</v>
+      </c>
+      <c r="E12">
+        <v>13.02</v>
+      </c>
+      <c r="F12">
+        <v>42.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>40</v>
+      </c>
+      <c r="B13">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="C13">
+        <v>44.03</v>
+      </c>
+      <c r="D13">
+        <v>47.9</v>
+      </c>
+      <c r="E13">
+        <v>14.25</v>
+      </c>
+      <c r="F13">
+        <v>45.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>42</v>
+      </c>
+      <c r="B14">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="C14">
+        <v>46.44</v>
+      </c>
+      <c r="D14">
+        <v>50.15</v>
+      </c>
+      <c r="E14">
+        <v>15.62</v>
+      </c>
+      <c r="F14">
+        <v>47.54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>44</v>
+      </c>
+      <c r="B15">
+        <v>0.505</v>
+      </c>
+      <c r="C15">
+        <v>48.85</v>
+      </c>
+      <c r="D15">
+        <v>52.4</v>
+      </c>
+      <c r="E15">
+        <v>17.11</v>
+      </c>
+      <c r="F15">
+        <v>49.91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>0.48</v>
+      </c>
+      <c r="C16">
+        <v>51.25</v>
+      </c>
+      <c r="D16">
+        <v>54.65</v>
+      </c>
+      <c r="E16">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="F16">
+        <v>52.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>48</v>
+      </c>
+      <c r="B17">
+        <v>0.46</v>
+      </c>
+      <c r="C17">
+        <v>53.66</v>
+      </c>
+      <c r="D17">
+        <v>56.9</v>
+      </c>
+      <c r="E17">
+        <v>20.48</v>
+      </c>
+      <c r="F17">
+        <v>54.63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>50</v>
+      </c>
+      <c r="B18">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="C18">
+        <v>56.07</v>
+      </c>
+      <c r="D18">
+        <v>59.15</v>
+      </c>
+      <c r="E18">
+        <v>22.45</v>
+      </c>
+      <c r="F18">
+        <v>56.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>